--- a/stockpredict/road_map_version_11.xlsx
+++ b/stockpredict/road_map_version_11.xlsx
@@ -926,7 +926,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress (Day 1/3 — reversal patterns done)</t>
         </is>
       </c>
     </row>

--- a/stockpredict/road_map_version_11.xlsx
+++ b/stockpredict/road_map_version_11.xlsx
@@ -3167,7 +3167,7 @@
       </c>
       <c r="J2" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="J4" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>In Progress (Day 1/3 — reversal patterns done)</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>

--- a/stockpredict/road_map_version_11.xlsx
+++ b/stockpredict/road_map_version_11.xlsx
@@ -973,7 +973,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>

--- a/stockpredict/road_map_version_11.xlsx
+++ b/stockpredict/road_map_version_11.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3843,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="J26" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="J28" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4727,7 +4727,7 @@
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4779,7 +4779,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4987,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5143,7 +5143,7 @@
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
